--- a/Plotting/Results_excels/result_data_long_Scope1-2_FPO.xlsx
+++ b/Plotting/Results_excels/result_data_long_Scope1-2_FPO.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,13 +483,6 @@
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Iteration_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -542,21 +535,6 @@
           <t>2050</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -581,47 +559,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_1\20250912073357_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20251124_11_02\Iteration_1\20251124161630_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_1\20250912082425_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20251124_11_02\Iteration_1\20251124170347_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_1\20250912101525_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20251124_11_02\Iteration_1\20251124185534_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_2\20250912135914_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20251124_11_02\Iteration_2\20251125012022_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_2\20250912144252_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20251124_11_02\Iteration_2\20251125021148_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_2\20250912154609_2050_minC_DD10-1\optimization_results.h5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_3\20250912192639_2030_minC_DD10-1\optimization_results.h5</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_3\20250912200933_2040_minC_DD10-1\optimization_results.h5</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20250912_04_01\Iteration_3\20250912215331_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\IESA_Scope3\Scope1-2\Results_model_linking_20251124_11_02\Iteration_2\20251125040242_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
     </row>
@@ -641,31 +604,22 @@
         <v>1732322014.983746</v>
       </c>
       <c r="E5" t="n">
-        <v>2691361916.541294</v>
+        <v>2686367318.442642</v>
       </c>
       <c r="F5" t="n">
-        <v>1602823033.003056</v>
+        <v>1637257166.321558</v>
       </c>
       <c r="G5" t="n">
-        <v>2052201453.570107</v>
+        <v>1714493983.898243</v>
       </c>
       <c r="H5" t="n">
-        <v>2700008437.015725</v>
+        <v>2688306476.18316</v>
       </c>
       <c r="I5" t="n">
-        <v>1608652531.723532</v>
+        <v>1640726973.152268</v>
       </c>
       <c r="J5" t="n">
-        <v>2036729438.842358</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2697557986.797098</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1611222603.246779</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2041727055.294393</v>
+        <v>1711505852.067703</v>
       </c>
     </row>
     <row r="6">
@@ -683,24 +637,17 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>404047658.3711658</v>
+        <v>404047658.37375</v>
       </c>
       <c r="G6" t="n">
-        <v>491202595.8345733</v>
+        <v>490692351.2505617</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>406223818.2045253</v>
+        <v>403892507.4703718</v>
       </c>
       <c r="J6" t="n">
-        <v>495003469.8000465</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>404047658.3823778</v>
-      </c>
-      <c r="M6" t="n">
-        <v>490390028.8761798</v>
+        <v>490887213.2623304</v>
       </c>
     </row>
     <row r="7">
@@ -719,31 +666,22 @@
         <v>2133745977.87842</v>
       </c>
       <c r="E7" t="n">
-        <v>2691361916.541294</v>
+        <v>2686367318.442642</v>
       </c>
       <c r="F7" t="n">
-        <v>2006870691.374222</v>
+        <v>2041304824.695308</v>
       </c>
       <c r="G7" t="n">
-        <v>2543404049.40468</v>
+        <v>2205186335.148805</v>
       </c>
       <c r="H7" t="n">
-        <v>2700008437.015725</v>
+        <v>2688306476.18316</v>
       </c>
       <c r="I7" t="n">
-        <v>2014876349.928057</v>
+        <v>2044619480.62264</v>
       </c>
       <c r="J7" t="n">
-        <v>2531732908.642405</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2697557986.797098</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2015270261.629157</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2532117084.170573</v>
+        <v>2202393065.330033</v>
       </c>
     </row>
     <row r="8">
@@ -760,17 +698,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>68375889989.4903</v>
+        <v>65288108199.13006</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>68403938773.81662</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>68408976742.1445</v>
+        <v>65314265146.65462</v>
       </c>
     </row>
     <row r="9">
@@ -789,30 +722,21 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1056578.591663621</v>
+        <v>1068528.536997583</v>
       </c>
       <c r="F9" t="n">
-        <v>82023.0237860162</v>
+        <v>90283.86473036271</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1070992.245706412</v>
+        <v>1059276.62120196</v>
       </c>
       <c r="I9" t="n">
-        <v>78949.00971633388</v>
+        <v>80316.33011693804</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1066045.908677773</v>
-      </c>
-      <c r="L9" t="n">
-        <v>77624.93973457512</v>
-      </c>
-      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -832,31 +756,22 @@
         <v>84709978.61488359</v>
       </c>
       <c r="E10" t="n">
-        <v>404047658.3711658</v>
+        <v>404047658.37375</v>
       </c>
       <c r="F10" t="n">
-        <v>87154937.46340746</v>
+        <v>86644692.87681174</v>
       </c>
       <c r="G10" t="n">
-        <v>92994207.68721794</v>
+        <v>93508819.57643567</v>
       </c>
       <c r="H10" t="n">
-        <v>406223818.2045253</v>
+        <v>403892507.4703718</v>
       </c>
       <c r="I10" t="n">
-        <v>88779651.59552123</v>
+        <v>86994705.79195862</v>
       </c>
       <c r="J10" t="n">
-        <v>93630185.53610204</v>
-      </c>
-      <c r="K10" t="n">
-        <v>404047658.3823778</v>
-      </c>
-      <c r="L10" t="n">
-        <v>86342370.49380201</v>
-      </c>
-      <c r="M10" t="n">
-        <v>93295882.66657615</v>
+        <v>93599809.32415968</v>
       </c>
     </row>
     <row r="11">
@@ -875,31 +790,22 @@
         <v>229503815.7670274</v>
       </c>
       <c r="E11" t="n">
-        <v>276718309.6221449</v>
+        <v>276718309.6225892</v>
       </c>
       <c r="F11" t="n">
-        <v>218691898.311243</v>
+        <v>218461937.5328737</v>
       </c>
       <c r="G11" t="n">
-        <v>255432936.5058358</v>
+        <v>255477644.6449766</v>
       </c>
       <c r="H11" t="n">
-        <v>277426090.4669892</v>
+        <v>276652062.2075979</v>
       </c>
       <c r="I11" t="n">
-        <v>219833233.4324556</v>
+        <v>218559179.0292805</v>
       </c>
       <c r="J11" t="n">
-        <v>256913717.5021388</v>
-      </c>
-      <c r="K11" t="n">
-        <v>276718309.6217563</v>
-      </c>
-      <c r="L11" t="n">
-        <v>218438502.478323</v>
-      </c>
-      <c r="M11" t="n">
-        <v>255340556.3694021</v>
+        <v>255623450.8532109</v>
       </c>
     </row>
     <row r="12">
@@ -918,31 +824,22 @@
         <v>1418108220.601835</v>
       </c>
       <c r="E12" t="n">
-        <v>1849890344.755944</v>
+        <v>1843078159.968969</v>
       </c>
       <c r="F12" t="n">
-        <v>1284500495.310553</v>
+        <v>1318418360.086384</v>
       </c>
       <c r="G12" t="n">
-        <v>1703774309.377053</v>
+        <v>1365507519.676831</v>
       </c>
       <c r="H12" t="n">
-        <v>1853460607.772262</v>
+        <v>1846645932.420371</v>
       </c>
       <c r="I12" t="n">
-        <v>1288031502.317701</v>
+        <v>1322956974.520242</v>
       </c>
       <c r="J12" t="n">
-        <v>1686185535.804117</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1854646436.083071</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1294634976.941025</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1693090616.258415</v>
+        <v>1362282591.890332</v>
       </c>
     </row>
     <row r="13">
@@ -961,30 +858,21 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>160705603.7920398</v>
+        <v>162523190.4773337</v>
       </c>
       <c r="F13" t="n">
-        <v>12475701.91785306</v>
+        <v>13732175.82548817</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>162897920.571948</v>
+        <v>161115974.0848184</v>
       </c>
       <c r="I13" t="n">
-        <v>12008144.37785438</v>
+        <v>12216113.81078628</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>162145582.7098928</v>
-      </c>
-      <c r="L13" t="n">
-        <v>11806753.33362888</v>
-      </c>
-      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1010,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1318.722560432772</v>
+        <v>1326.020131995595</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1019,16 +907,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1327.741165769088</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1323.00052381201</v>
+        <v>1327.310428921803</v>
       </c>
     </row>
     <row r="15">
@@ -1050,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>31.59451925482167</v>
+        <v>31.62744897368414</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1059,18 +938,9 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>31.87056114068675</v>
+        <v>31.53031071073991</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>31.47001459667393</v>
-      </c>
-      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1107,15 +977,6 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1150,15 +1011,6 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1176,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>628.7238301059012</v>
+        <v>628.7238300900925</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1185,21 +1037,12 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>618.8492638067925</v>
+        <v>628.7238300899411</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>628.7238301210257</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1219,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>676.5329554212805</v>
+        <v>676.5329554232063</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1228,21 +1071,12 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>586.2813812223319</v>
+        <v>660.8597712166886</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>676.5329554211821</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1268,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>199.0225220283762</v>
+        <v>197.9155015995161</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1277,16 +1111,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>200.7702628330238</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>198.244688124114</v>
+        <v>198.8713640031256</v>
       </c>
     </row>
     <row r="21">
@@ -1320,15 +1145,6 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1353,11 +1169,6 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1380,11 +1191,6 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1417,15 +1223,6 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1452,11 +1249,6 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1481,11 +1273,6 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1520,15 +1307,6 @@
       <c r="J27" t="n">
         <v>0</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1546,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4012.320629254938</v>
+        <v>4012.320629268566</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1555,21 +1333,12 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4045.080769279364</v>
+        <v>4012.320629268981</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4012.320629241737</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1592,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>909.1947986999041</v>
+        <v>910.142416508896</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1601,18 +1370,9 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>917.1384500917051</v>
+        <v>907.3470708126591</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>905.6119308395375</v>
-      </c>
-      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1649,15 +1409,6 @@
       <c r="J30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1692,15 +1443,6 @@
       <c r="J31" t="n">
         <v>1248</v>
       </c>
-      <c r="K31" t="n">
-        <v>1248</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1248</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1248</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1735,15 +1477,6 @@
       <c r="J32" t="n">
         <v>0</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1778,15 +1511,6 @@
       <c r="J33" t="n">
         <v>0</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1804,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>617.5001571631069</v>
+        <v>617.5001571650722</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1813,21 +1537,12 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>622.5419754728633</v>
+        <v>617.5001571651273</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>617.5001571627664</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1847,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>750.3039576705913</v>
+        <v>750.3039576732359</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1856,21 +1571,12 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>756.4301038552928</v>
+        <v>750.3039576732994</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>750.303957667864</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1895,11 +1601,6 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1924,11 +1625,6 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1963,15 +1659,6 @@
       <c r="J38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1989,31 +1676,22 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>123.4769063712205</v>
+        <v>123.4927342693412</v>
       </c>
       <c r="F39" t="n">
-        <v>3.980879510804559</v>
+        <v>3.97502751147964</v>
       </c>
       <c r="G39" t="n">
-        <v>10.50179638063998</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>123.6829593312197</v>
+        <v>123.3716356542447</v>
       </c>
       <c r="I39" t="n">
-        <v>4.53581468410995</v>
+        <v>4.021893517905744</v>
       </c>
       <c r="J39" t="n">
-        <v>12.44999049794457</v>
-      </c>
-      <c r="K39" t="n">
-        <v>123.6063268711243</v>
-      </c>
-      <c r="L39" t="n">
-        <v>4.034251968987717</v>
-      </c>
-      <c r="M39" t="n">
-        <v>10.26561107504728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2047,15 +1725,6 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2080,11 +1749,6 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -2107,11 +1771,6 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -2142,13 +1801,6 @@
         <v>0</v>
       </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>1068</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2179,13 +1831,6 @@
         <v>0</v>
       </c>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -2220,15 +1865,6 @@
       <c r="J45" t="n">
         <v>0</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -2249,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>3472.674904302246</v>
+        <v>3033.894106409309</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2258,18 +1894,9 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>2987.8975409142</v>
+        <v>3103.111378859075</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>2715.009794624744</v>
-      </c>
-      <c r="M46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2289,31 +1916,22 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>7.669420163986878e-10</v>
+        <v>3.915374691132456e-10</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>165.7731398274046</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1.959645907964084e-10</v>
       </c>
       <c r="I47" t="n">
-        <v>4.534014141872149</v>
+        <v>11.6516661211477</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>6.894981461488036e-09</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.131232352236111e-06</v>
-      </c>
-      <c r="M47" t="n">
-        <v>-1.138214297883236e-06</v>
       </c>
     </row>
     <row r="48">
@@ -2335,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>183.0839304671333</v>
+        <v>216.656373210691</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2344,18 +1962,9 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>185.596549382377</v>
+        <v>185.0581426983223</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.458310464302291e-08</v>
-      </c>
-      <c r="L48" t="n">
-        <v>182.3624512041966</v>
-      </c>
-      <c r="M48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2375,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>5756.853584676502</v>
+        <v>5756.853584690212</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2384,21 +1993,12 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>5699.362150501696</v>
+        <v>5741.18040048588</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>5756.853584662919</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2435,15 +2035,6 @@
       <c r="J50" t="n">
         <v>0</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -2461,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>750.3039576706735</v>
+        <v>750.3039576732359</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2470,21 +2061,12 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>756.4301038552928</v>
+        <v>750.3039576733019</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>750.3039576682048</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2521,15 +2103,6 @@
       <c r="J52" t="n">
         <v>0</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -2547,30 +2120,21 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>71.47200008008413</v>
+        <v>71.47200000048738</v>
       </c>
       <c r="F53" t="n">
-        <v>50.04945594030235</v>
+        <v>51.21588225885966</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>71.47200000105636</v>
+        <v>71.47200000023456</v>
       </c>
       <c r="I53" t="n">
-        <v>106.8874836849175</v>
+        <v>103.7806675289286</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>71.47200015637998</v>
-      </c>
-      <c r="L53" t="n">
-        <v>103.4043595477612</v>
-      </c>
-      <c r="M53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2596,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>199.0225220283763</v>
+        <v>197.9155015995161</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2605,16 +2169,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>200.770262833024</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>198.244688124114</v>
+        <v>198.8713640031256</v>
       </c>
     </row>
     <row r="55">
@@ -2650,15 +2205,6 @@
       <c r="J55" t="n">
         <v>0</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2693,15 +2239,6 @@
       <c r="J56" t="n">
         <v>0</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -2736,15 +2273,6 @@
       <c r="J57" t="n">
         <v>0</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2779,15 +2307,6 @@
       <c r="J58" t="n">
         <v>0</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2822,15 +2341,6 @@
       <c r="J59" t="n">
         <v>0</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2865,15 +2375,6 @@
       <c r="J60" t="n">
         <v>0</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2908,15 +2409,6 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2951,15 +2443,6 @@
       <c r="J62" t="n">
         <v>0</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2977,31 +2460,22 @@
         <v>128.5109405853489</v>
       </c>
       <c r="E63" t="n">
-        <v>123.4769063712205</v>
+        <v>123.4927342693412</v>
       </c>
       <c r="F63" t="n">
-        <v>127.4577858820305</v>
+        <v>127.467761780821</v>
       </c>
       <c r="G63" t="n">
-        <v>137.959582262665</v>
+        <v>127.4677617808208</v>
       </c>
       <c r="H63" t="n">
-        <v>123.6829593312197</v>
+        <v>123.3716356542447</v>
       </c>
       <c r="I63" t="n">
-        <v>128.2187740153463</v>
+        <v>127.3935291721505</v>
       </c>
       <c r="J63" t="n">
-        <v>140.6687645132742</v>
-      </c>
-      <c r="K63" t="n">
-        <v>123.6063268711243</v>
-      </c>
-      <c r="L63" t="n">
-        <v>127.6405788401465</v>
-      </c>
-      <c r="M63" t="n">
-        <v>137.9061899151594</v>
+        <v>127.3935291721504</v>
       </c>
     </row>
     <row r="64">
@@ -3037,15 +2511,6 @@
       <c r="J64" t="n">
         <v>0</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -3063,31 +2528,22 @@
         <v>139.8283576466475</v>
       </c>
       <c r="E65" t="n">
-        <v>136.5416640215674</v>
+        <v>136.5416640002884</v>
       </c>
       <c r="F65" t="n">
-        <v>152.7447261815839</v>
+        <v>152.9039259734946</v>
       </c>
       <c r="G65" t="n">
-        <v>139.6904742964129</v>
+        <v>152.9039259734949</v>
       </c>
       <c r="H65" t="n">
-        <v>136.5416640004815</v>
+        <v>136.5416640000734</v>
       </c>
       <c r="I65" t="n">
-        <v>154.0792596154065</v>
+        <v>152.4343078965267</v>
       </c>
       <c r="J65" t="n">
-        <v>141.4107815239487</v>
-      </c>
-      <c r="K65" t="n">
-        <v>136.541664011046</v>
-      </c>
-      <c r="L65" t="n">
-        <v>152.1428043810423</v>
-      </c>
-      <c r="M65" t="n">
-        <v>140.1400527793209</v>
+        <v>142.2170275534405</v>
       </c>
     </row>
     <row r="66">
@@ -3123,15 +2579,6 @@
       <c r="J66" t="n">
         <v>0</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -3166,15 +2613,6 @@
       <c r="J67" t="n">
         <v>0</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -3209,15 +2647,6 @@
       <c r="J68" t="n">
         <v>0</v>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -3252,15 +2681,6 @@
       <c r="J69" t="n">
         <v>0</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -3278,31 +2698,22 @@
         <v>4428.929286757269</v>
       </c>
       <c r="E70" t="n">
-        <v>1900.000000374978</v>
+        <v>1900.000000020453</v>
       </c>
       <c r="F70" t="n">
-        <v>3037.759582894448</v>
+        <v>3047.966659174694</v>
       </c>
       <c r="G70" t="n">
-        <v>4423.720002552353</v>
+        <v>4422.25256464655</v>
       </c>
       <c r="H70" t="n">
-        <v>1900</v>
+        <v>1900.000000000985</v>
       </c>
       <c r="I70" t="n">
-        <v>3071.092769849396</v>
+        <v>3036.044895946638</v>
       </c>
       <c r="J70" t="n">
-        <v>4466.17246404436</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1900.000000288063</v>
-      </c>
-      <c r="L70" t="n">
-        <v>3028.894910203589</v>
-      </c>
-      <c r="M70" t="n">
-        <v>4419.010133316151</v>
+        <v>4430.726514372793</v>
       </c>
     </row>
     <row r="71">
@@ -3338,15 +2749,6 @@
       <c r="J71" t="n">
         <v>0</v>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -3381,15 +2783,6 @@
       <c r="J72" t="n">
         <v>0</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -3424,15 +2817,6 @@
       <c r="J73" t="n">
         <v>0</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -3467,15 +2851,6 @@
       <c r="J74" t="n">
         <v>0</v>
       </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -3493,31 +2868,22 @@
         <v>159.0214789703329</v>
       </c>
       <c r="E75" t="n">
-        <v>79.06314519805383</v>
+        <v>79.04731728103262</v>
       </c>
       <c r="F75" t="n">
-        <v>111.8815931452146</v>
+        <v>120.2152163404987</v>
       </c>
       <c r="G75" t="n">
-        <v>128.4060275479166</v>
+        <v>163.8116575808156</v>
       </c>
       <c r="H75" t="n">
-        <v>80.51080862406216</v>
+        <v>79.16841589591709</v>
       </c>
       <c r="I75" t="n">
-        <v>114.0747283906095</v>
+        <v>112.4880629861389</v>
       </c>
       <c r="J75" t="n">
-        <v>128.4027016673192</v>
-      </c>
-      <c r="K75" t="n">
-        <v>78.93372471953367</v>
-      </c>
-      <c r="L75" t="n">
-        <v>111.2297409788026</v>
-      </c>
-      <c r="M75" t="n">
-        <v>127.9911638849429</v>
+        <v>164.3870867477973</v>
       </c>
     </row>
     <row r="76">
@@ -3553,15 +2919,6 @@
       <c r="J76" t="n">
         <v>0</v>
       </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -3596,15 +2953,6 @@
       <c r="J77" t="n">
         <v>0</v>
       </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -3639,15 +2987,6 @@
       <c r="J78" t="n">
         <v>0</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -3682,15 +3021,6 @@
       <c r="J79" t="n">
         <v>0</v>
       </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -3708,31 +3038,22 @@
         <v>2412.734197482533</v>
       </c>
       <c r="E80" t="n">
-        <v>5756.853584677532</v>
+        <v>5756.853584694267</v>
       </c>
       <c r="F80" t="n">
-        <v>4012.320629255597</v>
+        <v>4012.320629268569</v>
       </c>
       <c r="G80" t="n">
-        <v>4012.320629255867</v>
+        <v>4012.320629268642</v>
       </c>
       <c r="H80" t="n">
-        <v>5699.362150502214</v>
+        <v>5741.180400486546</v>
       </c>
       <c r="I80" t="n">
-        <v>4045.080769279365</v>
+        <v>4012.320629268981</v>
       </c>
       <c r="J80" t="n">
-        <v>4045.080769279642</v>
-      </c>
-      <c r="K80" t="n">
-        <v>5756.853584792556</v>
-      </c>
-      <c r="L80" t="n">
-        <v>4012.320629241737</v>
-      </c>
-      <c r="M80" t="n">
-        <v>4012.320629253655</v>
+        <v>4012.320629268995</v>
       </c>
     </row>
     <row r="81">
@@ -3768,15 +3089,6 @@
       <c r="J81" t="n">
         <v>0</v>
       </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3811,15 +3123,6 @@
       <c r="J82" t="n">
         <v>0</v>
       </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -3854,15 +3157,6 @@
       <c r="J83" t="n">
         <v>0</v>
       </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -3897,15 +3191,6 @@
       <c r="J84" t="n">
         <v>0</v>
       </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -3940,15 +3225,6 @@
       <c r="J85" t="n">
         <v>0</v>
       </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -3983,15 +3259,6 @@
       <c r="J86" t="n">
         <v>0</v>
       </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -4026,15 +3293,6 @@
       <c r="J87" t="n">
         <v>0</v>
       </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -4069,15 +3327,6 @@
       <c r="J88" t="n">
         <v>0</v>
       </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -4112,15 +3361,6 @@
       <c r="J89" t="n">
         <v>0</v>
       </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -4155,15 +3395,6 @@
       <c r="J90" t="n">
         <v>0</v>
       </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -4181,31 +3412,22 @@
         <v>11.55613605712362</v>
       </c>
       <c r="E91" t="n">
-        <v>1.675234138227691e-10</v>
+        <v>1.547739264875184e-10</v>
       </c>
       <c r="F91" t="n">
-        <v>9.418784596142672</v>
+        <v>9.392440821052688</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4187845961562</v>
+        <v>9.392440821052716</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>1.048922838111009e-10</v>
       </c>
       <c r="I91" t="n">
-        <v>9.197951087450605</v>
+        <v>9.47015143140807</v>
       </c>
       <c r="J91" t="n">
-        <v>9.197951087450633</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2.347625239296839e-08</v>
-      </c>
-      <c r="L91" t="n">
-        <v>9.518388322660869</v>
-      </c>
-      <c r="M91" t="n">
-        <v>9.518388322660897</v>
+        <v>9.470151431408254</v>
       </c>
     </row>
     <row r="92">
@@ -4241,15 +3463,6 @@
       <c r="J92" t="n">
         <v>0</v>
       </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -4284,15 +3497,6 @@
       <c r="J93" t="n">
         <v>0</v>
       </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -4327,15 +3531,6 @@
       <c r="J94" t="n">
         <v>0</v>
       </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -4370,15 +3565,6 @@
       <c r="J95" t="n">
         <v>0</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -4413,15 +3599,6 @@
       <c r="J96" t="n">
         <v>0</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -4456,15 +3633,6 @@
       <c r="J97" t="n">
         <v>0</v>
       </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -4499,15 +3667,6 @@
       <c r="J98" t="n">
         <v>0</v>
       </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -4542,15 +3701,6 @@
       <c r="J99" t="n">
         <v>0</v>
       </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -4585,15 +3735,6 @@
       <c r="J100" t="n">
         <v>0</v>
       </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -4628,15 +3769,6 @@
       <c r="J101" t="n">
         <v>0</v>
       </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -4671,15 +3803,6 @@
       <c r="J102" t="n">
         <v>0</v>
       </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -4712,15 +3835,6 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4739,24 +3853,17 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>628.7238301059012</v>
+        <v>628.7238300900925</v>
       </c>
       <c r="G104" t="n">
-        <v>628.7238301059012</v>
+        <v>628.7238300900925</v>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>618.8492638067925</v>
+        <v>628.7238300899411</v>
       </c>
       <c r="J104" t="n">
-        <v>618.8492638067925</v>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="n">
-        <v>628.7238301210257</v>
-      </c>
-      <c r="M104" t="n">
-        <v>628.7238301210257</v>
+        <v>628.7238300899411</v>
       </c>
     </row>
     <row r="105">
@@ -4774,24 +3881,17 @@
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
-        <v>676.5329554212805</v>
+        <v>676.5329554232063</v>
       </c>
       <c r="G105" t="n">
-        <v>676.5329554212805</v>
+        <v>676.5329554232063</v>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>586.2813812223319</v>
+        <v>660.8597712166886</v>
       </c>
       <c r="J105" t="n">
-        <v>586.2813812223319</v>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="n">
-        <v>676.5329554211821</v>
-      </c>
-      <c r="M105" t="n">
-        <v>676.5329554211821</v>
+        <v>660.8597712166886</v>
       </c>
     </row>
     <row r="106">
@@ -4809,23 +3909,16 @@
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
-        <v>106.0225220283762</v>
+        <v>104.9155015995161</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>107.7702628330238</v>
+        <v>105.8713640031255</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="n">
-        <v>105.244688124111</v>
-      </c>
-      <c r="M106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4854,13 +3947,6 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4879,24 +3965,17 @@
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
-        <v>123.4769063712205</v>
+        <v>123.4927342693412</v>
       </c>
       <c r="G108" t="n">
-        <v>127.457785882025</v>
+        <v>127.4677617808208</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>123.6829593312197</v>
+        <v>123.3716356542447</v>
       </c>
       <c r="J108" t="n">
-        <v>128.2187740153296</v>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="n">
-        <v>123.6063268711243</v>
-      </c>
-      <c r="M108" t="n">
-        <v>127.6405788401121</v>
+        <v>127.3935291721504</v>
       </c>
     </row>
     <row r="109">
@@ -4915,17 +3994,12 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>3472.674904302246</v>
+        <v>3033.894106409309</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>2987.8975409142</v>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="n">
-        <v>2715.009794624744</v>
+        <v>3103.111378859075</v>
       </c>
     </row>
     <row r="110">
@@ -4943,24 +4017,17 @@
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>5756.853584676502</v>
+        <v>5756.853584690212</v>
       </c>
       <c r="G110" t="n">
-        <v>5756.853584676502</v>
+        <v>5756.853584690212</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>5699.362150501696</v>
+        <v>5741.18040048588</v>
       </c>
       <c r="J110" t="n">
-        <v>5699.362150501696</v>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="n">
-        <v>5756.853584662919</v>
-      </c>
-      <c r="M110" t="n">
-        <v>5756.853584662919</v>
+        <v>5741.18040048588</v>
       </c>
     </row>
     <row r="111">
@@ -4977,17 +4044,12 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>31.59451925482167</v>
+        <v>31.62744897368414</v>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>31.87056114068675</v>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="n">
-        <v>31.47001459667393</v>
+        <v>31.53031071073991</v>
       </c>
     </row>
     <row r="112">
@@ -5007,9 +4069,6 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -5025,17 +4084,12 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>106.0225220283762</v>
+        <v>104.9155015995161</v>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>107.7702628330238</v>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="n">
-        <v>105.244688124111</v>
+        <v>105.8713640031255</v>
       </c>
     </row>
     <row r="114">
@@ -5051,24 +4105,17 @@
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
-        <v>4012.320629254938</v>
+        <v>4012.320629268566</v>
       </c>
       <c r="G114" t="n">
-        <v>4012.320629254938</v>
+        <v>4012.320629268566</v>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>4045.080769279364</v>
+        <v>4012.320629268981</v>
       </c>
       <c r="J114" t="n">
-        <v>4045.080769279364</v>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="n">
-        <v>4012.320629241737</v>
-      </c>
-      <c r="M114" t="n">
-        <v>4012.320629241737</v>
+        <v>4012.320629268981</v>
       </c>
     </row>
     <row r="115">
@@ -5085,17 +4132,12 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>909.1947986999041</v>
+        <v>910.142416508896</v>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>917.1384500917051</v>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="n">
-        <v>905.6119308395375</v>
+        <v>907.3470708126591</v>
       </c>
     </row>
     <row r="116">
@@ -5111,24 +4153,17 @@
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>617.5001571631069</v>
+        <v>617.5001571650722</v>
       </c>
       <c r="G116" t="n">
-        <v>617.5001571631069</v>
+        <v>617.5001571650722</v>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>622.5419754728633</v>
+        <v>617.5001571651273</v>
       </c>
       <c r="J116" t="n">
-        <v>622.5419754728633</v>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="n">
-        <v>617.5001571627664</v>
-      </c>
-      <c r="M116" t="n">
-        <v>617.5001571627664</v>
+        <v>617.5001571651273</v>
       </c>
     </row>
     <row r="117">
@@ -5144,24 +4179,17 @@
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
-        <v>750.3039576705913</v>
+        <v>750.3039576732359</v>
       </c>
       <c r="G117" t="n">
-        <v>750.3039576705913</v>
+        <v>750.3039576732359</v>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>756.4301038552928</v>
+        <v>750.3039576732994</v>
       </c>
       <c r="J117" t="n">
-        <v>756.4301038552928</v>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="n">
-        <v>750.303957667864</v>
-      </c>
-      <c r="M117" t="n">
-        <v>750.303957667864</v>
+        <v>750.3039576732994</v>
       </c>
     </row>
     <row r="118">
@@ -5177,24 +4205,17 @@
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>750.3039576706735</v>
+        <v>750.3039576732359</v>
       </c>
       <c r="G118" t="n">
-        <v>750.3039576706735</v>
+        <v>750.3039576732359</v>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>756.4301038552928</v>
+        <v>750.3039576733019</v>
       </c>
       <c r="J118" t="n">
-        <v>756.4301038552928</v>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="n">
-        <v>750.3039576682048</v>
-      </c>
-      <c r="M118" t="n">
-        <v>750.3039576682048</v>
+        <v>750.3039576733019</v>
       </c>
     </row>
     <row r="119">
@@ -5208,22 +4229,17 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>7.669420163986878e-10</v>
+        <v>3.915374691132456e-10</v>
       </c>
       <c r="G119" t="n">
-        <v>7.669420163986878e-10</v>
+        <v>165.7731398277962</v>
       </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>1.959645907964084e-10</v>
+      </c>
       <c r="J119" t="n">
-        <v>4.534014141872149</v>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="n">
-        <v>6.894981461488036e-09</v>
-      </c>
-      <c r="M119" t="n">
-        <v>1.138127333697599e-06</v>
+        <v>11.65166612134366</v>
       </c>
     </row>
     <row r="120">
@@ -5238,27 +4254,19 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>183.0839304671333</v>
+        <v>216.656373210691</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>185.596549382377</v>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="n">
-        <v>2.458310464302291e-08</v>
-      </c>
-      <c r="M120" t="n">
-        <v>182.3624512287797</v>
+        <v>185.0581426983223</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
